--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2280,6 +2280,112 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120441682</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90843</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>73</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Veckticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Flavidoporia pulvinascens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storbackens naturreservat, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>609062</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6949670</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gustaf Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gustaf Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>126674026</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>126673580</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>126673814</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>126674026</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>126673580</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>126673814</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2391,7 +2391,7 @@
         <v>126674026</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>126673580</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>126673814</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17276194</v>
+        <v>120441682</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens naturreservat, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609161.1374973198</v>
+        <v>609062</v>
       </c>
       <c r="R2" t="n">
-        <v>6949492.999514189</v>
+        <v>6949670</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,42 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Gustaf Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Gustaf Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>17270953</v>
       </c>
       <c r="B3" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608845.6768441275</v>
+        <v>608846</v>
       </c>
       <c r="R3" t="n">
-        <v>6949588.840406776</v>
+        <v>6949589</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +848,9 @@
           <t>2013-08-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17270952</v>
+        <v>53489539</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +897,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608845.6768441275</v>
+        <v>608802</v>
       </c>
       <c r="R4" t="n">
-        <v>6949588.840406776</v>
+        <v>6949672</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -999,22 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-09-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,7 +974,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Aspskog</t>
+          <t>SCA Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1039,7 +985,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
+          <t>Tomas Rydkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,57 +996,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17270956</v>
+        <v>131106904</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbacken SV sluttningen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608845.6768441275</v>
+        <v>608801</v>
       </c>
       <c r="R5" t="n">
-        <v>6949588.840406776</v>
+        <v>6949348</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,24 +1064,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2025_0268</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ullticka på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,62 +1102,52 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Aspskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
+          <t>Jennifer Lehikoinen, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17270955</v>
+        <v>68622743</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>1642</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1215,17 +1157,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens NR, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608845.6768441275</v>
+        <v>609099</v>
       </c>
       <c r="R6" t="n">
-        <v>6949588.840406776</v>
+        <v>6949678</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,62 +1207,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Aspskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Johan Rytterstam</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Rytterstam</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17270957</v>
+        <v>68622828</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1642</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1340,17 +1258,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens NR, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608845.6768441275</v>
+        <v>609065</v>
       </c>
       <c r="R7" t="n">
-        <v>6949588.840406776</v>
+        <v>6949657</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,22 +1292,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,62 +1308,48 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Aspskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Johan Rytterstam</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Rytterstam</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17276192</v>
+        <v>68622829</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1642</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1465,17 +1359,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens NR, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609161.1374973198</v>
+        <v>609072</v>
       </c>
       <c r="R8" t="n">
-        <v>6949492.999514189</v>
+        <v>6949664</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,22 +1393,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,62 +1409,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Johan Rytterstam</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Rytterstam</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17270911</v>
+        <v>68622830</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1642</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1590,17 +1460,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens NR, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609161.1374973198</v>
+        <v>609124</v>
       </c>
       <c r="R9" t="n">
-        <v>6949492.999514189</v>
+        <v>6949645</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1624,22 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,62 +1510,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Johan Rytterstam</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Rytterstam</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>53489539</v>
+        <v>68622835</v>
       </c>
       <c r="B10" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>1642</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1715,17 +1561,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens NR, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608801.9272496389</v>
+        <v>608992</v>
       </c>
       <c r="R10" t="n">
-        <v>6949672.489372145</v>
+        <v>6949758</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1749,22 +1595,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>1997-09-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1997-09-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,62 +1611,48 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>SCA Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Johan Rytterstam</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Rytterstam</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>53489538</v>
+        <v>17270911</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1844,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>608801.9272496389</v>
+        <v>609161</v>
       </c>
       <c r="R11" t="n">
-        <v>6949672.489372145</v>
+        <v>6949493</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1874,22 +1696,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1997-09-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1997-09-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,7 +1715,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>SCA Skogsmark</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1914,7 +1726,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Via Caroline Westerlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1925,37 +1737,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>53489537</v>
+        <v>17270957</v>
       </c>
       <c r="B12" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1969,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>608801.9272496389</v>
+        <v>608846</v>
       </c>
       <c r="R12" t="n">
-        <v>6949672.489372145</v>
+        <v>6949589</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -1999,22 +1806,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1997-09-02</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1997-09-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,7 +1825,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>SCA Skogsmark</t>
+          <t>Aspskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2039,7 +1836,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
+          <t>Via Caroline Westerlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2050,57 +1847,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68622829</v>
+        <v>131106920</v>
       </c>
       <c r="B13" t="n">
-        <v>77713</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1642</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storbackens NR, Mpd</t>
+          <t>Storbacken sv sluttningen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609072.1201438464</v>
+        <v>608789</v>
       </c>
       <c r="R13" t="n">
-        <v>6949663.923061803</v>
+        <v>6949370</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2122,24 +1919,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2025_0251</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2154,69 +1961,73 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Rytterstam</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Rytterstam</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Alexander Hoffmann, Jennifer Lehikoinen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68622828</v>
+        <v>131106982</v>
       </c>
       <c r="B14" t="n">
-        <v>77713</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1642</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storbackens NR, Mpd</t>
+          <t>Storbacken SV sluttningen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609064.9861426172</v>
+        <v>608674</v>
       </c>
       <c r="R14" t="n">
-        <v>6949656.788284697</v>
+        <v>6949490</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2238,24 +2049,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2025_0187</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2270,27 +2091,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Rytterstam</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Rytterstam</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Jennifer Lehikoinen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120441682</v>
+        <v>131106919</v>
       </c>
       <c r="B15" t="n">
-        <v>90937</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,40 +2118,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storbackens naturreservat, Mpd</t>
+          <t>Storbacken sv sluttningen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609062</v>
+        <v>608800</v>
       </c>
       <c r="R15" t="n">
-        <v>6949670</v>
+        <v>6949358</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2353,14 +2179,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2025_0252</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2369,29 +2215,32 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Gustaf Nilsson</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gustaf Nilsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Alexander Hoffmann, Jennifer Lehikoinen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126674026</v>
+        <v>131106927</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,39 +2248,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbacken SV sluttningen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609077</v>
+        <v>608755</v>
       </c>
       <c r="R16" t="n">
-        <v>6949581</v>
+        <v>6949365</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2456,19 +2309,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2025_0244</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Vedskivlav på silverlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,50 +2351,53 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alexander Hoffmann, Jennifer Lehikoinen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126673580</v>
+        <v>17270956</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2535,13 +2406,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609143</v>
+        <v>608846</v>
       </c>
       <c r="R17" t="n">
-        <v>6949552</v>
+        <v>6949589</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2565,17 +2436,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,26 +2452,35 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Aspskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126673814</v>
+        <v>16000651</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,45 +2488,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609189</v>
+        <v>609154</v>
       </c>
       <c r="R18" t="n">
-        <v>6949475</v>
+        <v>6949620</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2675,17 +2544,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,15 +2569,1596 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17270952</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>608846</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6949589</v>
+      </c>
+      <c r="S19" t="n">
+        <v>100</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Aspskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>53489538</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>608802</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6949672</v>
+      </c>
+      <c r="S20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1997-09-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1997-09-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>SCA Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Rydkvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131106915</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storbacken sv sluttningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>608815</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6949365</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2025_0256</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Hoffmann, Jennifer Lehikoinen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126673580</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>609143</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6949552</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126673814</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>609189</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6949475</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126674026</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>609077</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6949581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131106986</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storbacken SV sluttningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>608662</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6949490</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2025_0183</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre spår av ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jennifer Lehikoinen, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131106978</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storbacken SV sluttningen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>608701</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6949456</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2025_0191</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Myllgrop vid rotvälta. Färska spår av tjäder</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jennifer Lehikoinen, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>17276192</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>609161</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6949493</v>
+      </c>
+      <c r="S27" t="n">
+        <v>100</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131106963</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nordost om Högsttjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>608825</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6949336</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2025_0207</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Granskogsbrant</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tove von Euler, Pattranit Kwanruen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>17276194</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609161</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6949493</v>
+      </c>
+      <c r="S29" t="n">
+        <v>100</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16000645</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>609157</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6949616</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2014-06-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2014-06-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2014-06-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>17270955</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>608846</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6949589</v>
+      </c>
+      <c r="S31" t="n">
+        <v>100</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Aspskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>53489537</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>608802</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6949672</v>
+      </c>
+      <c r="S32" t="n">
+        <v>100</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1997-09-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1997-09-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>SCA Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Rydkvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53489539</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106904</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,6 +1053,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106920</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1168,6 +1188,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1298,6 +1323,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1538,6 +1573,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53489538</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1668,6 +1708,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106915</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1789,6 +1834,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106986</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1910,6 +1960,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106978</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2018,6 +2073,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53489537</t>
         </is>
       </c>
     </row>
@@ -2121,6 +2181,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120441682</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2231,6 +2296,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270953</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2332,6 +2402,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622743</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2433,6 +2508,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622828</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2534,6 +2614,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622829</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2635,6 +2720,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622830</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2736,6 +2826,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622835</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2846,6 +2941,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270911</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2956,6 +3056,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270957</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3066,6 +3171,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270956</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3170,6 +3280,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16000651</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3280,6 +3395,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270952</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3387,6 +3507,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673580</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3497,6 +3622,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126673814</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3604,6 +3734,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3714,6 +3849,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276192</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3835,6 +3975,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131106963</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3945,6 +4090,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17276194</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4049,6 +4199,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16000645</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4159,8 +4314,46 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270955</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2304,52 +2304,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68622743</v>
+        <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>79526</v>
+        <v>92454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1642</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Långskägg</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Usnea longissima</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storbackens NR, Mpd</t>
+          <t>Indalsälven, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609099</v>
+        <v>608967</v>
       </c>
       <c r="R15" t="n">
-        <v>6949678</v>
+        <v>6949572</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2373,12 +2369,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2015-06-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2015-06-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2393,24 +2389,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Rytterstam</t>
+          <t>Henrik Möller</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Rytterstam</t>
+          <t>Henrik Möller</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68622743</t>
+          <t>https://artportalen.se/Sighting/136456627</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68622828</v>
+        <v>68622743</v>
       </c>
       <c r="B16" t="n">
         <v>79526</v>
@@ -2449,10 +2445,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609065</v>
+        <v>609099</v>
       </c>
       <c r="R16" t="n">
-        <v>6949657</v>
+        <v>6949678</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2510,13 +2506,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68622828</t>
+          <t>https://artportalen.se/Sighting/68622743</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68622829</v>
+        <v>68622828</v>
       </c>
       <c r="B17" t="n">
         <v>79526</v>
@@ -2555,10 +2551,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609072</v>
+        <v>609065</v>
       </c>
       <c r="R17" t="n">
-        <v>6949664</v>
+        <v>6949657</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2616,13 +2612,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68622829</t>
+          <t>https://artportalen.se/Sighting/68622828</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68622830</v>
+        <v>68622829</v>
       </c>
       <c r="B18" t="n">
         <v>79526</v>
@@ -2661,10 +2657,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609124</v>
+        <v>609072</v>
       </c>
       <c r="R18" t="n">
-        <v>6949645</v>
+        <v>6949664</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2722,13 +2718,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68622830</t>
+          <t>https://artportalen.se/Sighting/68622829</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68622835</v>
+        <v>68622830</v>
       </c>
       <c r="B19" t="n">
         <v>79526</v>
@@ -2767,10 +2763,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>608992</v>
+        <v>609124</v>
       </c>
       <c r="R19" t="n">
-        <v>6949758</v>
+        <v>6949645</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2828,38 +2824,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68622835</t>
+          <t>https://artportalen.se/Sighting/68622830</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17270911</v>
+        <v>68622835</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>79526</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1642</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Långskägg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea longissima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2869,17 +2865,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Storbackens NR, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609161</v>
+        <v>608992</v>
       </c>
       <c r="R20" t="n">
-        <v>6949493</v>
+        <v>6949758</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2903,12 +2899,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2015-06-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2015-06-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2919,37 +2915,28 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Johan Rytterstam</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Rytterstam</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17270911</t>
+          <t>https://artportalen.se/Sighting/68622835</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>17270957</v>
+        <v>17270911</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2988,10 +2975,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608846</v>
+        <v>609161</v>
       </c>
       <c r="R21" t="n">
-        <v>6949589</v>
+        <v>6949493</v>
       </c>
       <c r="S21" t="n">
         <v>100</v>
@@ -3037,7 +3024,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Aspskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3058,38 +3045,38 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17270957</t>
+          <t>https://artportalen.se/Sighting/17270911</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>17270956</v>
+        <v>17270957</v>
       </c>
       <c r="B22" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3173,56 +3160,58 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17270956</t>
+          <t>https://artportalen.se/Sighting/17270957</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16000651</v>
+        <v>17270956</v>
       </c>
       <c r="B23" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609154</v>
+        <v>608846</v>
       </c>
       <c r="R23" t="n">
-        <v>6949620</v>
+        <v>6949589</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3246,17 +3235,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-06-16</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-06-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2014-06-16</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3267,28 +3251,37 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Aspskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Salmonsson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Salmonsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16000651</t>
+          <t>https://artportalen.se/Sighting/17270956</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>17270952</v>
+        <v>16000651</v>
       </c>
       <c r="B24" t="n">
         <v>80432</v>
@@ -3316,24 +3309,22 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>608846</v>
+        <v>609154</v>
       </c>
       <c r="R24" t="n">
-        <v>6949589</v>
+        <v>6949620</v>
       </c>
       <c r="S24" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3357,12 +3348,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2014-06-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3373,40 +3369,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Aspskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Jonas Salmonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17270952</t>
+          <t>https://artportalen.se/Sighting/16000651</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126673580</v>
+        <v>17270952</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3414,27 +3401,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3443,13 +3429,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609143</v>
+        <v>608846</v>
       </c>
       <c r="R25" t="n">
-        <v>6949552</v>
+        <v>6949589</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3473,17 +3459,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3494,28 +3475,37 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Aspskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126673580</t>
+          <t>https://artportalen.se/Sighting/17270952</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126673814</v>
+        <v>126673580</v>
       </c>
       <c r="B26" t="n">
         <v>57953</v>
@@ -3544,24 +3534,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609189</v>
+        <v>609143</v>
       </c>
       <c r="R26" t="n">
-        <v>6949475</v>
+        <v>6949552</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3624,13 +3611,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126673814</t>
+          <t>https://artportalen.se/Sighting/126673580</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126674026</v>
+        <v>126673814</v>
       </c>
       <c r="B27" t="n">
         <v>57953</v>
@@ -3659,21 +3646,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609077</v>
+        <v>609189</v>
       </c>
       <c r="R27" t="n">
-        <v>6949581</v>
+        <v>6949475</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3736,43 +3726,44 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126674026</t>
+          <t>https://artportalen.se/Sighting/126673814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>17276192</v>
+        <v>126674026</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3781,13 +3772,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609161</v>
+        <v>609077</v>
       </c>
       <c r="R28" t="n">
-        <v>6949493</v>
+        <v>6949581</v>
       </c>
       <c r="S28" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3811,12 +3802,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3827,78 +3823,73 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17276192</t>
+          <t>https://artportalen.se/Sighting/126674026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131106963</v>
+        <v>17276192</v>
       </c>
       <c r="B29" t="n">
-        <v>106243</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Nordost om Högsttjärnen, Mpd</t>
+          <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>608825</v>
+        <v>609161</v>
       </c>
       <c r="R29" t="n">
-        <v>6949336</v>
+        <v>6949493</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3920,34 +3911,14 @@
           <t>Ljustorp</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>2025_0207</t>
-        </is>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Granskogsbrant</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3958,35 +3929,40 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tove von Euler, Pattranit Kwanruen</t>
+          <t>Via Caroline Westerlund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Kustpaketet</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131106963</t>
+          <t>https://artportalen.se/Sighting/17276192</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17276194</v>
+        <v>131106963</v>
       </c>
       <c r="B30" t="n">
-        <v>101326</v>
+        <v>106243</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3994,41 +3970,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storbacken, Mpd</t>
+          <t>Nordost om Högsttjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609161</v>
+        <v>608825</v>
       </c>
       <c r="R30" t="n">
-        <v>6949493</v>
+        <v>6949336</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4050,14 +4022,34 @@
           <t>Ljustorp</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2025_0207</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Granskogsbrant</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4068,40 +4060,35 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
+          <t>Tove von Euler, Pattranit Kwanruen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kustpaketet</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17276194</t>
+          <t>https://artportalen.se/Sighting/131106963</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>16000645</v>
+        <v>17276194</v>
       </c>
       <c r="B31" t="n">
-        <v>80392</v>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4109,39 +4096,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609157</v>
+        <v>609161</v>
       </c>
       <c r="R31" t="n">
-        <v>6949616</v>
+        <v>6949493</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4165,17 +4154,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2014-06-16</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2014-06-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2014-06-16</t>
+          <t>2013-08-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4186,28 +4170,37 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonas Salmonsson</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jonas Salmonsson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16000645</t>
+          <t>https://artportalen.se/Sighting/17276194</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17270955</v>
+        <v>16000645</v>
       </c>
       <c r="B32" t="n">
         <v>80392</v>
@@ -4235,24 +4228,22 @@
           <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storbacken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>608846</v>
+        <v>609157</v>
       </c>
       <c r="R32" t="n">
-        <v>6949589</v>
+        <v>6949616</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4276,12 +4267,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2013-08-12</t>
+          <t>2014-06-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2014-06-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4292,29 +4288,135 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Aspskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jonas Salmonsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16000645</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>17270955</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storbacken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>608846</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6949589</v>
+      </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2013-08-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Aspskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Caroline Westerlund</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Via Caroline Westerlund</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
+      <c r="AY33" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/17270955</t>
         </is>
@@ -4353,6 +4455,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55927-2023 artfynd.xlsx
+++ b/artfynd/A 55927-2023 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>136456627</v>
       </c>
       <c r="B15" t="n">
-        <v>92454</v>
+        <v>92455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
